--- a/final_geotwin_results.xlsx
+++ b/final_geotwin_results.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>AI_RQI_V3</t>
+          <t>AI_RQI</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
